--- a/Configs/GameConfig/Datas/soldier_visual.xlsx
+++ b/Configs/GameConfig/Datas/soldier_visual.xlsx
@@ -2,7 +2,7 @@
 <file path=xl/workbook.xml><?xml version="1.0" encoding="utf-8"?>
 <x:workbook xmlns:x="http://schemas.openxmlformats.org/spreadsheetml/2006/main">
   <x:sheets>
-    <x:sheet xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" name="TbSoldierVisual" sheetId="1" r:id="R238080e5d1d64ede"/>
+    <x:sheet xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" name="TbSoldierVisual" sheetId="1" r:id="Rd217e1dec9bb4bae"/>
   </x:sheets>
 </x:workbook>
 </file>
@@ -359,29 +359,27 @@
         <x:v>id</x:v>
       </x:c>
       <x:c r="C1" t="str">
-        <x:v>animationKey</x:v>
+        <x:v>bodyLocalOffset</x:v>
       </x:c>
       <x:c r="D1" t="str">
-        <x:v>bodyLocalOffset</x:v>
+        <x:v>hitEffectPointOffset</x:v>
       </x:c>
       <x:c r="E1" t="str">
-        <x:v>hitEffectPointOffset</x:v>
+        <x:v>projectileOriginOffset</x:v>
       </x:c>
       <x:c r="F1" t="str">
-        <x:v>projectileOriginOffset</x:v>
+        <x:v>weaponPivotOffset</x:v>
       </x:c>
       <x:c r="G1" t="str">
-        <x:v>weaponPivotOffset</x:v>
+        <x:v>defaultFacing</x:v>
       </x:c>
       <x:c r="H1" t="str">
-        <x:v>defaultFacing</x:v>
+        <x:v>hasWeaponPivot</x:v>
       </x:c>
       <x:c r="I1" t="str">
-        <x:v>hasWeaponPivot</x:v>
-      </x:c>
-      <x:c r="J1" t="str">
         <x:v>hasProjectileOrigin</x:v>
       </x:c>
+      <x:c r="J1"/>
     </x:row>
     <x:row r="2">
       <x:c r="A2" t="str">
@@ -391,7 +389,7 @@
         <x:v>int</x:v>
       </x:c>
       <x:c r="C2" t="str">
-        <x:v>string</x:v>
+        <x:v>vector2</x:v>
       </x:c>
       <x:c r="D2" t="str">
         <x:v>vector2</x:v>
@@ -403,30 +401,44 @@
         <x:v>vector2</x:v>
       </x:c>
       <x:c r="G2" t="str">
-        <x:v>vector2</x:v>
+        <x:v>int</x:v>
       </x:c>
       <x:c r="H2" t="str">
-        <x:v>int</x:v>
+        <x:v>bool</x:v>
       </x:c>
       <x:c r="I2" t="str">
         <x:v>bool</x:v>
       </x:c>
-      <x:c r="J2" t="str">
-        <x:v>bool</x:v>
-      </x:c>
+      <x:c r="J2"/>
     </x:row>
     <x:row r="3">
       <x:c r="A3" t="str">
         <x:v>##</x:v>
       </x:c>
-      <x:c r="B3"/>
-      <x:c r="C3"/>
-      <x:c r="D3"/>
-      <x:c r="E3"/>
-      <x:c r="F3"/>
-      <x:c r="G3"/>
-      <x:c r="H3"/>
-      <x:c r="I3"/>
+      <x:c r="B3" t="str">
+        <x:v>主键</x:v>
+      </x:c>
+      <x:c r="C3" t="str">
+        <x:v>Body 偏移，世界单位</x:v>
+      </x:c>
+      <x:c r="D3" t="str">
+        <x:v>受击特效挂点偏移，世界单位</x:v>
+      </x:c>
+      <x:c r="E3" t="str">
+        <x:v>箭矢出生点偏移，仅弓兵有值</x:v>
+      </x:c>
+      <x:c r="F3" t="str">
+        <x:v>武器挂点偏移，仅枪兵有值</x:v>
+      </x:c>
+      <x:c r="G3" t="str">
+        <x:v>默认朝向：1=右 / -1=左</x:v>
+      </x:c>
+      <x:c r="H3" t="str">
+        <x:v>是否有武器挂点，仅枪兵为 true</x:v>
+      </x:c>
+      <x:c r="I3" t="str">
+        <x:v>是否有投射物原点，仅弓兵为 true</x:v>
+      </x:c>
       <x:c r="J3"/>
     </x:row>
     <x:row r="4">
@@ -447,31 +459,15 @@
       <x:c r="A5" t="str">
         <x:v>##</x:v>
       </x:c>
-      <x:c r="B5" t="str">
-        <x:v>ID(主键)</x:v>
-      </x:c>
+      <x:c r="B5"/>
       <x:c r="C5"/>
-      <x:c r="D5" t="str">
-        <x:v>Body偏移(世界单位)</x:v>
-      </x:c>
-      <x:c r="E5" t="str">
-        <x:v>受击特效挂点偏移(世界单位)</x:v>
-      </x:c>
-      <x:c r="F5" t="str">
-        <x:v>箭矢出生点偏移(世界单位)</x:v>
-      </x:c>
-      <x:c r="G5" t="str">
-        <x:v>武器挂点偏移(世界单位)</x:v>
-      </x:c>
-      <x:c r="H5" t="str">
-        <x:v>默认朝向(1=右,-1=左)</x:v>
-      </x:c>
-      <x:c r="I5" t="str">
-        <x:v>是否有武器挂点(仅枪兵)</x:v>
-      </x:c>
-      <x:c r="J5" t="str">
-        <x:v>是否有投射物原点(仅弓兵)</x:v>
-      </x:c>
+      <x:c r="D5"/>
+      <x:c r="E5"/>
+      <x:c r="F5"/>
+      <x:c r="G5"/>
+      <x:c r="H5"/>
+      <x:c r="I5"/>
+      <x:c r="J5"/>
     </x:row>
     <x:row r="6">
       <x:c r="A6"/>
@@ -479,29 +475,27 @@
         <x:v>1</x:v>
       </x:c>
       <x:c r="C6" t="str">
-        <x:v>knife</x:v>
+        <x:v>-0.166071,0.50625</x:v>
       </x:c>
       <x:c r="D6" t="str">
-        <x:v>-0.166071,0.50625</x:v>
+        <x:v>0,0.295625</x:v>
       </x:c>
       <x:c r="E6" t="str">
-        <x:v>0,0.295625</x:v>
+        <x:v>0,0</x:v>
       </x:c>
       <x:c r="F6" t="str">
         <x:v>0,0</x:v>
       </x:c>
-      <x:c r="G6" t="str">
-        <x:v>0,0</x:v>
-      </x:c>
-      <x:c r="H6" t="n">
+      <x:c r="G6" t="n">
         <x:v>1</x:v>
       </x:c>
-      <x:c r="I6" t="str">
+      <x:c r="H6" t="str">
         <x:v>false</x:v>
       </x:c>
-      <x:c r="J6" s="1" t="b">
+      <x:c r="I6" s="1" t="b">
         <x:v>0</x:v>
       </x:c>
+      <x:c r="J6"/>
     </x:row>
     <x:row r="7">
       <x:c r="A7"/>
@@ -509,29 +503,27 @@
         <x:v>2</x:v>
       </x:c>
       <x:c r="C7" t="str">
-        <x:v>bow</x:v>
+        <x:v>0.03125,0.1</x:v>
       </x:c>
       <x:c r="D7" t="str">
-        <x:v>0.03125,0.1</x:v>
+        <x:v>0,0.32125</x:v>
       </x:c>
       <x:c r="E7" t="str">
-        <x:v>0,0.32125</x:v>
+        <x:v>0.16875,0.38875</x:v>
       </x:c>
       <x:c r="F7" t="str">
-        <x:v>0.16875,0.38875</x:v>
-      </x:c>
-      <x:c r="G7" t="str">
         <x:v>0,0</x:v>
       </x:c>
-      <x:c r="H7" t="n">
+      <x:c r="G7" t="n">
         <x:v>1</x:v>
       </x:c>
-      <x:c r="I7" t="str">
+      <x:c r="H7" t="str">
         <x:v>false</x:v>
       </x:c>
-      <x:c r="J7" s="1" t="b">
+      <x:c r="I7" s="1" t="b">
         <x:v>1</x:v>
       </x:c>
+      <x:c r="J7"/>
     </x:row>
     <x:row r="8">
       <x:c r="A8"/>
@@ -539,29 +531,27 @@
         <x:v>3</x:v>
       </x:c>
       <x:c r="C8" t="str">
-        <x:v>pike</x:v>
+        <x:v>0.11875,0.35</x:v>
       </x:c>
       <x:c r="D8" t="str">
-        <x:v>0.11875,0.35</x:v>
+        <x:v>0,0.34375</x:v>
       </x:c>
       <x:c r="E8" t="str">
-        <x:v>0,0.34375</x:v>
+        <x:v>0,0</x:v>
       </x:c>
       <x:c r="F8" t="str">
-        <x:v>0,0</x:v>
-      </x:c>
-      <x:c r="G8" t="str">
         <x:v>-0.2125,0.45</x:v>
       </x:c>
-      <x:c r="H8" t="n">
+      <x:c r="G8" t="n">
         <x:v>1</x:v>
       </x:c>
-      <x:c r="I8" t="str">
+      <x:c r="H8" t="str">
         <x:v>true</x:v>
       </x:c>
-      <x:c r="J8" s="1" t="b">
+      <x:c r="I8" s="1" t="b">
         <x:v>0</x:v>
       </x:c>
+      <x:c r="J8"/>
     </x:row>
     <x:row r="9">
       <x:c r="A9"/>
@@ -569,29 +559,27 @@
         <x:v>4</x:v>
       </x:c>
       <x:c r="C9" t="str">
-        <x:v>cavalry</x:v>
+        <x:v>0,0.375</x:v>
       </x:c>
       <x:c r="D9" t="str">
-        <x:v>0,0.375</x:v>
+        <x:v>0,0.378125</x:v>
       </x:c>
       <x:c r="E9" t="str">
-        <x:v>0,0.378125</x:v>
+        <x:v>0,0</x:v>
       </x:c>
       <x:c r="F9" t="str">
         <x:v>0,0</x:v>
       </x:c>
-      <x:c r="G9" t="str">
-        <x:v>0,0</x:v>
-      </x:c>
-      <x:c r="H9" t="n">
+      <x:c r="G9" t="n">
         <x:v>1</x:v>
       </x:c>
-      <x:c r="I9" t="str">
+      <x:c r="H9" t="str">
         <x:v>false</x:v>
       </x:c>
-      <x:c r="J9" s="1" t="b">
+      <x:c r="I9" s="1" t="b">
         <x:v>0</x:v>
       </x:c>
+      <x:c r="J9"/>
     </x:row>
   </x:sheetData>
   <x:pageMargins left="0.7" right="0.7" top="0.75" bottom="0.75" header="0.3" footer="0.3"/>
